--- a/2026/Proyecto_Final/drive_proyecto_final/Técnico/PCP.xlsx
+++ b/2026/Proyecto_Final/drive_proyecto_final/Técnico/PCP.xlsx
@@ -65,24 +65,24 @@
     <t>prod x semana</t>
   </si>
   <si>
+    <t>Kg x  turno</t>
+  </si>
+  <si>
+    <t>TURNO DISPONIBLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turno x semana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan de molde </t>
+  </si>
+  <si>
     <t>Turnos disponibles x semana</t>
   </si>
   <si>
     <t xml:space="preserve">Capacidad del horno </t>
   </si>
   <si>
-    <t>Kg x  turno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turno x semana </t>
-  </si>
-  <si>
-    <t>TURNO DISPONIBLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan de molde </t>
-  </si>
-  <si>
     <t xml:space="preserve">horas activas al año </t>
   </si>
   <si>
@@ -110,55 +110,73 @@
     <t>kg/hora</t>
   </si>
   <si>
+    <t>Turno x semana</t>
+  </si>
+  <si>
+    <t>Kg x turno</t>
+  </si>
+  <si>
+    <t>Kg x hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas disponibles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">hr </t>
+  </si>
+  <si>
     <t xml:space="preserve">turnos </t>
   </si>
   <si>
-    <t>Turno x semana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horas disponibles </t>
-  </si>
-  <si>
-    <t>Kg x turno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hr </t>
+    <t>SEMANAS DE PRODUCCIÓN</t>
   </si>
   <si>
     <t xml:space="preserve">Frecuencia </t>
   </si>
   <si>
-    <t>Kg x hora</t>
-  </si>
-  <si>
-    <t>SEMANAS DE PRODUCCIÓN</t>
-  </si>
-  <si>
     <t xml:space="preserve">libres </t>
   </si>
   <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>kg x semana</t>
+  </si>
+  <si>
     <t>15 dias</t>
   </si>
   <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>kg x semana</t>
-  </si>
-  <si>
     <t>Turnos / mes</t>
   </si>
   <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tiempo limpieza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">min / turno </t>
+  </si>
+  <si>
+    <t>Turnos /mes</t>
+  </si>
+  <si>
+    <t>Chocolate con chips picante 150gr.</t>
+  </si>
+  <si>
     <t>SEMANA 1/3</t>
   </si>
   <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>S3</t>
+    <t>Pan de molde 400gr.</t>
   </si>
   <si>
     <t>Pan de molde</t>
@@ -167,24 +185,12 @@
     <t>TM</t>
   </si>
   <si>
-    <t>S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tiempo limpieza </t>
-  </si>
-  <si>
     <t xml:space="preserve">Lunes </t>
   </si>
   <si>
-    <t xml:space="preserve">min / turno </t>
-  </si>
-  <si>
     <t>Martes</t>
   </si>
   <si>
-    <t>Chocolate con chips picante 150gr.</t>
-  </si>
-  <si>
     <t>Miércoles</t>
   </si>
   <si>
@@ -200,9 +206,6 @@
     <t xml:space="preserve">PAN </t>
   </si>
   <si>
-    <t>Turnos /mes</t>
-  </si>
-  <si>
     <t>BUDIN</t>
   </si>
   <si>
@@ -215,16 +218,22 @@
     <t>TN</t>
   </si>
   <si>
-    <t>Pan de molde 400gr.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Budines vainilla </t>
   </si>
   <si>
+    <t>Galletitas símil chocolinas free 150gr.</t>
+  </si>
+  <si>
     <t>Largada/ paradas NP</t>
   </si>
   <si>
-    <t>Galletitas símil chocolinas free 150gr.</t>
+    <t>Budines vainilla/cítricos 180gr.</t>
+  </si>
+  <si>
+    <t>Galletitas símil chocolinas 150gr.</t>
+  </si>
+  <si>
+    <t>Budines chocolate 180gr.</t>
   </si>
   <si>
     <t xml:space="preserve">hr disponible x turno </t>
@@ -233,13 +242,13 @@
     <t>SEMANA 2/4</t>
   </si>
   <si>
-    <t>Galletitas símil chocolinas 150gr.</t>
+    <t>Pepas chocolate y batata 150gr.</t>
   </si>
   <si>
     <t xml:space="preserve">kg x turno </t>
   </si>
   <si>
-    <t>Budines vainilla/cítricos 180gr.</t>
+    <t>Bizcochos sabor queso free 150gr.</t>
   </si>
   <si>
     <t>LUNES</t>
@@ -260,9 +269,6 @@
     <t xml:space="preserve">Info </t>
   </si>
   <si>
-    <t>Pepas chocolate y batata 150gr.</t>
-  </si>
-  <si>
     <t>Stock 20 dias</t>
   </si>
   <si>
@@ -281,13 +287,13 @@
     <t xml:space="preserve">2 veces al mes </t>
   </si>
   <si>
-    <t>Budines chocolate 180gr.</t>
+    <t>Bizcochos sabor queso 150gr.</t>
   </si>
   <si>
     <t xml:space="preserve">Pepas </t>
   </si>
   <si>
-    <t>Bizcochos sabor queso free 150gr.</t>
+    <t>Polvorones free 150gr.</t>
   </si>
   <si>
     <t xml:space="preserve">Bizcochos </t>
@@ -299,6 +305,9 @@
     <t xml:space="preserve">Polvorones </t>
   </si>
   <si>
+    <t>Polvorones 150gr.</t>
+  </si>
+  <si>
     <t>SEMANA 2</t>
   </si>
   <si>
@@ -308,21 +317,15 @@
     <t>Chips</t>
   </si>
   <si>
-    <t>Bizcochos sabor queso 150gr.</t>
-  </si>
-  <si>
     <t>20 dias de stock</t>
   </si>
   <si>
-    <t>Polvorones free 150gr.</t>
-  </si>
-  <si>
-    <t>Polvorones 150gr.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cajas por turno </t>
   </si>
   <si>
+    <t>Cajas x dia</t>
+  </si>
+  <si>
     <t>Cajas x pallet</t>
   </si>
   <si>
@@ -335,7 +338,7 @@
     <t>Pallets x semana</t>
   </si>
   <si>
-    <t>Cajas x dia</t>
+    <t>Palets x dia</t>
   </si>
   <si>
     <t>Pallets x semana galletitas</t>
@@ -348,9 +351,6 @@
   </si>
   <si>
     <t>Altura del pallet</t>
-  </si>
-  <si>
-    <t>Palets x dia</t>
   </si>
   <si>
     <t>Ancho del pallet</t>
@@ -695,11 +695,11 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -710,14 +710,16 @@
     </xf>
     <xf borderId="7" fillId="3" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="20" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="20" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -728,40 +730,38 @@
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="3" fontId="3" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="3" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="2" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="7" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="7" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -769,15 +769,15 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1047,30 +1047,30 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3">
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
         <v>63.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="7">
         <v>359000.0</v>
       </c>
@@ -1085,13 +1085,13 @@
         <f>+B2/D2</f>
         <v>7510.460251</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>15.0</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>5736.0</v>
       </c>
     </row>
@@ -1100,19 +1100,19 @@
         <f>+E2/F2</f>
         <v>500.6973501</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>76.0</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1129,73 +1129,73 @@
       <c r="J4" s="14"/>
     </row>
     <row r="5">
-      <c r="K5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="K5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="2">
         <v>8.0</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="24"/>
+      <c r="A6" s="15"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="29" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="H7" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="I7" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="31" t="s">
         <v>40</v>
-      </c>
-      <c r="M7" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="33" t="s">
-        <v>44</v>
       </c>
       <c r="B8" s="12">
         <v>101000.0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f t="shared" ref="C8:C15" si="1">+B8/12</f>
         <v>8416.666667</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f t="shared" ref="D8:D15" si="2">+C8/4</f>
         <v>2104.166667</v>
       </c>
@@ -1203,40 +1203,40 @@
         <f t="shared" ref="E8:E15" si="3">+C8/$F$3</f>
         <v>16.80988858</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>8.0</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="36">
+      <c r="G8" s="17"/>
+      <c r="H8" s="35">
         <v>9.0</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="3">
+      <c r="I8" s="17"/>
+      <c r="J8" s="2">
         <f t="shared" ref="J8:J15" si="4">+SUM(F8:I8)</f>
         <v>17</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="K8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="2">
         <v>15.0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>42</v>
+      <c r="N8" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="33" t="s">
-        <v>58</v>
+      <c r="A9" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="B9" s="12">
         <v>13000.0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f t="shared" si="1"/>
         <v>1083.333333</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f t="shared" si="2"/>
         <v>270.8333333</v>
       </c>
@@ -1244,40 +1244,40 @@
         <f t="shared" si="3"/>
         <v>2.163649025</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>1.0</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18">
+      <c r="G9" s="17"/>
+      <c r="H9" s="17">
         <v>1.0</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="3">
+      <c r="I9" s="17"/>
+      <c r="J9" s="2">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="K9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="2">
         <v>30.0</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>42</v>
+      <c r="N9" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>61</v>
+      <c r="A10" s="31" t="s">
+        <v>60</v>
       </c>
       <c r="B10" s="12">
         <v>31000.0</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <f t="shared" si="1"/>
         <v>2583.333333</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f t="shared" si="2"/>
         <v>645.8333333</v>
       </c>
@@ -1285,15 +1285,15 @@
         <f t="shared" si="3"/>
         <v>5.159470752</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>3.0</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18">
+      <c r="G10" s="17"/>
+      <c r="H10" s="17">
         <v>2.0</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="3">
+      <c r="I10" s="17"/>
+      <c r="J10" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -1301,22 +1301,22 @@
         <f>+(M5*60-M7-M8-M9)/60</f>
         <v>6.916666667</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>59</v>
+      <c r="N10" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="33" t="s">
-        <v>70</v>
+      <c r="A11" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="B11" s="12">
         <v>94000.0</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <f t="shared" si="1"/>
         <v>7833.333333</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <f t="shared" si="2"/>
         <v>1958.333333</v>
       </c>
@@ -1324,31 +1324,31 @@
         <f t="shared" si="3"/>
         <v>15.6448468</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17">
         <v>8.0</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18">
+      <c r="H11" s="17"/>
+      <c r="I11" s="17">
         <v>8.0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="33" t="s">
-        <v>79</v>
+      <c r="A12" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="B12" s="12">
         <v>13000.0</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <f t="shared" si="1"/>
         <v>1083.333333</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <f t="shared" si="2"/>
         <v>270.8333333</v>
       </c>
@@ -1356,38 +1356,38 @@
         <f t="shared" si="3"/>
         <v>2.163649025</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>1.0</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18">
+      <c r="G12" s="17"/>
+      <c r="H12" s="17">
         <v>1.0</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="3">
+      <c r="I12" s="17"/>
+      <c r="J12" s="2">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f>+M3*M10</f>
         <v>525.6666667</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>62</v>
+      <c r="M12" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="33" t="s">
-        <v>86</v>
+      <c r="A13" s="31" t="s">
+        <v>79</v>
       </c>
       <c r="B13" s="12">
         <v>31000.0</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <f t="shared" si="1"/>
         <v>2583.333333</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <f t="shared" si="2"/>
         <v>645.8333333</v>
       </c>
@@ -1395,33 +1395,33 @@
         <f t="shared" si="3"/>
         <v>5.159470752</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>2.0</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18">
+      <c r="G13" s="17"/>
+      <c r="H13" s="17">
         <v>2.0</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <v>1.0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="33" t="s">
-        <v>88</v>
+      <c r="A14" s="31" t="s">
+        <v>81</v>
       </c>
       <c r="B14" s="12">
         <v>23000.0</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <f t="shared" si="1"/>
         <v>1916.666667</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <f t="shared" si="2"/>
         <v>479.1666667</v>
       </c>
@@ -1429,31 +1429,31 @@
         <f t="shared" si="3"/>
         <v>3.827994429</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17">
         <v>2.0</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18">
+      <c r="H14" s="17"/>
+      <c r="I14" s="17">
         <v>2.0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="33" t="s">
-        <v>89</v>
+      <c r="A15" s="31" t="s">
+        <v>85</v>
       </c>
       <c r="B15" s="12">
         <v>53000.0</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <f t="shared" si="1"/>
         <v>4416.666667</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <f t="shared" si="2"/>
         <v>1104.166667</v>
       </c>
@@ -1461,50 +1461,50 @@
         <f t="shared" si="3"/>
         <v>8.821030641</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17">
         <v>5.0</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18">
+      <c r="H15" s="17"/>
+      <c r="I15" s="17">
         <v>4.0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="17"/>
-      <c r="F16" s="3">
+      <c r="A16" s="15"/>
+      <c r="F16" s="2">
         <f t="shared" ref="F16:J16" si="5">+SUM(F8:F15)</f>
         <v>15</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="40">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="17"/>
+      <c r="A17" s="15"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="17"/>
+      <c r="A18" s="15"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="17"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="41" t="s">
         <v>90</v>
       </c>
@@ -1514,9 +1514,9 @@
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="17"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" s="44">
         <f>D20</f>
@@ -1526,94 +1526,94 @@
         <f>15*7</f>
         <v>105</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <f>0.24*6</f>
         <v>1.44</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="17"/>
-      <c r="B21" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="47">
+      <c r="A21" s="15"/>
+      <c r="B21" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="48">
         <f>ROUND(+C19/C20,0)</f>
         <v>2</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <f>C21*15</f>
         <v>30</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="17"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="45">
         <v>15.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="17"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="3">
+        <v>95</v>
+      </c>
+      <c r="C23" s="2">
         <f>C21*C22</f>
         <v>30</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="17"/>
+      <c r="A24" s="15"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="17"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="47">
+        <v>97</v>
+      </c>
+      <c r="C25" s="48">
         <f>C23</f>
         <v>30</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="17"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="47">
+        <v>98</v>
+      </c>
+      <c r="C26" s="48">
         <f>'Panificados ok'!F20</f>
         <v>10</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="17"/>
+      <c r="A27" s="15"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="17"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="47">
+        <v>99</v>
+      </c>
+      <c r="C28" s="48">
         <f>SUM(C25:C26)</f>
         <v>40</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="17"/>
+      <c r="A29" s="15"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="17"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="45">
         <v>1.85</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="17"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="45" t="s">
         <v>101</v>
       </c>
@@ -1622,7 +1622,7 @@
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="17"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="45" t="s">
         <v>102</v>
       </c>
@@ -1631,11 +1631,11 @@
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="17"/>
+      <c r="A33" s="15"/>
     </row>
     <row r="34">
-      <c r="A34" s="17"/>
-      <c r="B34" s="49" t="s">
+      <c r="A34" s="15"/>
+      <c r="B34" s="50" t="s">
         <v>103</v>
       </c>
       <c r="C34" s="45">
@@ -1649,11 +1649,11 @@
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="17"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="48">
         <f>C28</f>
         <v>40</v>
       </c>
@@ -1663,17 +1663,17 @@
       <c r="F35" s="45">
         <v>1.1</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <f>(F35*C36)/2</f>
         <v>7.15</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="17"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <f>ROUND(C35/C34,0)</f>
         <v>13</v>
       </c>
@@ -1685,61 +1685,61 @@
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="17"/>
+      <c r="A37" s="15"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="17"/>
+      <c r="A38" s="15"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="17"/>
+      <c r="A39" s="15"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="17"/>
+      <c r="A40" s="15"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="17"/>
+      <c r="A41" s="15"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="17"/>
+      <c r="A42" s="15"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="17"/>
+      <c r="A43" s="15"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="17"/>
+      <c r="A44" s="15"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="17"/>
+      <c r="A45" s="15"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="17"/>
+      <c r="A46" s="15"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="17"/>
+      <c r="A47" s="15"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="17"/>
+      <c r="A48" s="15"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="17"/>
+      <c r="A49" s="15"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="17"/>
+      <c r="A50" s="15"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="17"/>
+      <c r="A51" s="15"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="17"/>
+      <c r="A52" s="15"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="17"/>
+      <c r="A53" s="15"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="17"/>
+      <c r="A54" s="15"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="17"/>
+      <c r="A55" s="15"/>
     </row>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1"/>
@@ -2717,168 +2717,168 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
+      <c r="L1" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
         <v>118000.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>239.0</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <f t="shared" ref="D2:D3" si="1">+C2/5</f>
         <v>47.8</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f t="shared" ref="E2:E3" si="2">+B2/D2</f>
         <v>2468.619247</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="9"/>
       <c r="H2" s="10"/>
       <c r="I2" s="9"/>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <f>3*5</f>
         <v>15</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>202000.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>239.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f t="shared" si="1"/>
         <v>47.8</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <f t="shared" si="2"/>
         <v>4225.941423</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>23</v>
-      </c>
       <c r="H3" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>5736.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="25">
+      <c r="B4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="19">
         <f>+SUM(E2:E3)</f>
         <v>6694.560669</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="20">
         <v>15.0</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="25">
         <f>+$E$4/$F$4</f>
         <v>446.3040446</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="25">
         <f>+G4/M10</f>
         <v>66.11911772</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="26"/>
+      <c r="C5" s="27"/>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>50</v>
+      <c r="E6" s="27" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="H6" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="I6" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="K6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="2">
         <v>8.0</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2">
         <v>118000.0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f t="shared" ref="C7:C9" si="3">+B7/12</f>
         <v>9833.333333</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f t="shared" ref="D7:D9" si="4">+C7/4</f>
         <v>2458.333333</v>
       </c>
@@ -2886,44 +2886,44 @@
         <f t="shared" ref="E7:E9" si="5">+C7/$G$4</f>
         <v>22.0328125</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>6.0</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <v>5.0</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="35">
         <v>6.0</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <v>5.0</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" ref="J7:J9" si="6">+I7+H7+G7+F7</f>
         <v>22</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="2">
         <v>30.0</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>42</v>
+      <c r="N7" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2">
         <v>141000.0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f t="shared" si="3"/>
         <v>11750</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f t="shared" si="4"/>
         <v>2937.5</v>
       </c>
@@ -2931,44 +2931,44 @@
         <f t="shared" si="5"/>
         <v>26.32734375</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>6.0</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <v>7.0</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <v>6.0</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <v>7.5</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="6"/>
         <v>26.5</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="K8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="2">
         <v>15.0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>42</v>
+      <c r="N8" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2">
         <v>61000.0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f t="shared" si="3"/>
         <v>5083.333333</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f t="shared" si="4"/>
         <v>1270.833333</v>
       </c>
@@ -2976,50 +2976,50 @@
         <f t="shared" si="5"/>
         <v>11.38984375</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>3.0</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>3.0</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>3.0</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="17">
         <v>2.5</v>
       </c>
       <c r="J9" s="9">
         <f t="shared" si="6"/>
         <v>11.5</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="K9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="2">
         <v>30.0</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>42</v>
+      <c r="N9" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <f t="shared" ref="E10:I10" si="7">+SUM(E7:E9)</f>
         <v>59.75</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="35">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
@@ -3031,111 +3031,111 @@
         <f>+(M6*60-M7-M8-M9)/60</f>
         <v>6.75</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>59</v>
+      <c r="N10" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>12.0</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>0.18</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="38">
         <f>+A11*B11</f>
         <v>2.16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>6.0</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>0.4</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="38">
         <f>+$A$12*$B$12</f>
         <v>2.4</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3" t="s">
-        <v>62</v>
+      <c r="M12" s="5"/>
+      <c r="N12" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="18" t="s">
+      <c r="F13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="H13" s="17" t="s">
         <v>47</v>
       </c>
+      <c r="I13" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14">
-      <c r="F14" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="18" t="s">
+      <c r="F14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="H14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="F15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="G15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="F15" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="F16" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>51</v>
+      <c r="J16" s="17" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="48">
+      <c r="E17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="46">
         <f>+G4/C12</f>
         <v>185.9600186</v>
       </c>
@@ -3143,7 +3143,7 @@
         <f>+$G$4/$C$11</f>
         <v>206.6222429</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="46">
         <f>+G4/C12</f>
         <v>185.9600186</v>
       </c>
@@ -3157,10 +3157,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="50">
+      <c r="E18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="49">
         <f>ROUND(+F17/'Galletitas ok'!C20,0)</f>
         <v>2</v>
       </c>
@@ -3168,7 +3168,7 @@
         <f>ROUND(+G17/'Galletitas ok'!C20,0)</f>
         <v>2</v>
       </c>
-      <c r="H18" s="50">
+      <c r="H18" s="49">
         <f>ROUND(+H17/'Galletitas ok'!C20,0)</f>
         <v>2</v>
       </c>
@@ -3183,9 +3183,9 @@
     </row>
     <row r="20">
       <c r="E20" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="47">
+        <v>95</v>
+      </c>
+      <c r="F20" s="48">
         <f>SUM(F18:J18)</f>
         <v>10</v>
       </c>
@@ -4198,50 +4198,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>118000.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>239.0</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <f t="shared" ref="D2:D3" si="1">+C2/5</f>
         <v>47.8</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f t="shared" ref="E2:E3" si="2">+B2/D2</f>
         <v>2468.619247</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>+M12</f>
         <v>477.48</v>
       </c>
@@ -4250,33 +4250,33 @@
         <v>5.170099788</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <f>3*5</f>
         <v>15</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>202000.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>239.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f t="shared" si="1"/>
         <v>47.8</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <f t="shared" si="2"/>
         <v>4225.941423</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <f>+M12</f>
         <v>477.48</v>
       </c>
@@ -4285,23 +4285,23 @@
         <v>8.850509807</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>5736.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <f>+SUM(B2:B3)</f>
         <v>320000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f t="shared" ref="D4:E4" si="4">+SUM(D2:D3)</f>
         <v>95.6</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <f t="shared" si="4"/>
         <v>6694.560669</v>
       </c>
@@ -4309,240 +4309,240 @@
         <f>+G2+G3</f>
         <v>14.0206096</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>69.0</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="24"/>
+      <c r="C5" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="N7" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="18" t="s">
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="E8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="3">
+      <c r="D9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="2">
         <v>30.0</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N9" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>42</v>
+      <c r="O9" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
-      <c r="N10" s="35">
+      <c r="N10" s="36">
         <f>+N6-0.5-0.25-0.33</f>
         <v>6.92</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>59</v>
+      <c r="O10" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="24"/>
+      <c r="C11" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12">
-      <c r="C12" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="6">
+      <c r="F12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="5">
         <f>+N4*N10</f>
         <v>477.48</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>62</v>
+      <c r="N12" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="D13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="E13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="D14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="18" t="s">
+      <c r="D15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>51</v>
+      <c r="E15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5561,40 +5561,40 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3">
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2">
         <v>63.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>359000.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>239.0</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <f>+C2/5</f>
         <v>47.8</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f>+B2/D2</f>
         <v>7510.460251</v>
       </c>
@@ -5602,16 +5602,16 @@
         <f>+E2/K11</f>
         <v>14.2806135</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>110.0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>5736.0</v>
       </c>
     </row>
@@ -5626,47 +5626,47 @@
         <v>334.6</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="15">
+      <c r="F3" s="16">
         <v>12.0</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>76.0</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>81.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12"/>
-      <c r="B4" s="19"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="21">
+      <c r="F4" s="23">
         <v>3.0</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3">
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="2">
         <f>+N3*8</f>
         <v>654.4</v>
       </c>
@@ -5682,16 +5682,16 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="H5" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2">
         <v>8.0</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5705,14 +5705,14 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="J6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="J6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="2">
         <v>20.0</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>42</v>
+      <c r="M6" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -5726,19 +5726,19 @@
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-      <c r="H7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="H7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="2">
         <v>15.0</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P7" s="35"/>
+      <c r="M7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="36"/>
     </row>
     <row r="8">
       <c r="A8" s="12"/>
@@ -5751,14 +5751,14 @@
         <f>+F8+F9</f>
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="2">
         <v>30.0</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>42</v>
+      <c r="M8" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -5769,14 +5769,14 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="L9" s="35">
+      <c r="L9" s="36">
         <f>+L5-0.5-0.25-0.33</f>
         <v>6.92</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="M9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="2">
         <f>+L9/8</f>
         <v>0.865</v>
       </c>
@@ -5801,12 +5801,12 @@
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f>+L3*L9</f>
         <v>525.92</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>62</v>
+      <c r="L11" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -5819,245 +5819,245 @@
       <c r="G12" s="12"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L13" s="26" t="s">
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>71</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="F14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L14" s="3">
+      <c r="I14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="2">
         <v>3.0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>20</v>
+      <c r="M14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <v>6.0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>20</v>
+      <c r="M15" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="E16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L16" s="3">
+      <c r="I16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="2">
         <v>3.0</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>20</v>
+      <c r="M16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
-      <c r="I17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="I17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="2">
         <v>5.0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>20</v>
+      <c r="M17" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="B18" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="2">
         <v>6.0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>20</v>
+      <c r="M18" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="39" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>84</v>
+        <v>55</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -7071,79 +7071,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="3">
+      <c r="I1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="2">
         <v>94.6</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>359000.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <f>+B2/12</f>
         <v>29916.66667</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <f>+C2/4</f>
         <v>7479.166667</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>110.0</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>3.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="51" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B4" s="52">
         <v>101000.0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <f t="shared" ref="C4:C11" si="1">+B4/12</f>
         <v>8416.666667</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f t="shared" ref="D4:D11" si="2">+C4/4</f>
         <v>2104.166667</v>
       </c>
@@ -7151,19 +7151,19 @@
         <f t="shared" ref="E4:E11" si="3">+C4/$J$9</f>
         <v>11.86281419</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>7.5</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="54">
         <v>13000.0</v>
@@ -7180,24 +7180,24 @@
         <f t="shared" si="3"/>
         <v>1.526896876</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" ref="F5:F6" si="4">+C5/2</f>
         <v>541.6666667</v>
       </c>
-      <c r="G5" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="G5" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f>+J4*J3</f>
         <v>22.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="54">
         <v>31000.0</v>
@@ -7214,23 +7214,23 @@
         <f t="shared" si="3"/>
         <v>3.641061781</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="4"/>
         <v>1291.666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="56" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B7" s="57">
         <v>94000.0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f t="shared" si="1"/>
         <v>7833.333333</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f t="shared" si="2"/>
         <v>1958.333333</v>
       </c>
@@ -7238,29 +7238,29 @@
         <f t="shared" si="3"/>
         <v>11.04063895</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f>3*5*4</f>
         <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="56" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B8" s="57">
         <v>13000.0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f t="shared" si="1"/>
         <v>1083.333333</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f t="shared" si="2"/>
         <v>270.8333333</v>
       </c>
@@ -7275,16 +7275,16 @@
     </row>
     <row r="9">
       <c r="A9" s="56" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B9" s="57">
         <v>31000.0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f t="shared" si="1"/>
         <v>2583.333333</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f t="shared" si="2"/>
         <v>645.8333333</v>
       </c>
@@ -7292,26 +7292,26 @@
         <f t="shared" si="3"/>
         <v>3.641061781</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f>+J1*J4</f>
         <v>709.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="56" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B10" s="57">
         <v>23000.0</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <f t="shared" si="1"/>
         <v>1916.666667</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f t="shared" si="2"/>
         <v>479.1666667</v>
       </c>
@@ -7326,16 +7326,16 @@
     </row>
     <row r="11">
       <c r="A11" s="56" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B11" s="57">
         <v>53000.0</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <f t="shared" si="1"/>
         <v>4416.666667</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <f t="shared" si="2"/>
         <v>1104.166667</v>
       </c>
@@ -7345,242 +7345,242 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="E13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>71</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="E14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="3">
+      <c r="H14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="2">
         <v>3.0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>20</v>
+      <c r="L14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <v>6.0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>20</v>
+      <c r="L15" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="3">
+      <c r="H16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="2">
         <v>3.0</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>20</v>
+      <c r="L16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
-      <c r="H17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="H17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="2">
         <v>5.0</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>20</v>
+      <c r="L17" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="B18" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="2">
         <v>6.0</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>20</v>
+      <c r="L18" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="38" t="s">
+      <c r="E21" s="2" t="s">
         <v>87</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>84</v>
+        <v>55</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="26" t="s">
-        <v>33</v>
+      <c r="B24" s="27" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
